--- a/DATA/DATA FILES/WATER SOURCE HEAT PUMP DATA.xlsx
+++ b/DATA/DATA FILES/WATER SOURCE HEAT PUMP DATA.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF321"/>
+  <dimension ref="A1:AH321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,8 @@
     <col width="22" customWidth="1" min="28" max="28"/>
     <col width="14" customWidth="1" min="31" max="31"/>
     <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,12 +502,22 @@
       </c>
       <c r="AE2" s="1" t="inlineStr">
         <is>
-          <t>SUBMITTAL</t>
+          <t>PRODUCT DATA SHEET</t>
         </is>
       </c>
       <c r="AF2" s="1" t="inlineStr">
         <is>
           <t>ENGINEERING MANUAL</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="inlineStr">
+        <is>
+          <t>INSTALLATION MANUAL</t>
+        </is>
+      </c>
+      <c r="AH2" s="1" t="inlineStr">
+        <is>
+          <t>REVIT</t>
         </is>
       </c>
     </row>
@@ -755,6 +767,21 @@
       <c r="AC5" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -863,6 +890,21 @@
       <c r="AC6" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -971,6 +1013,21 @@
       <c r="AC7" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1079,6 +1136,21 @@
       <c r="AC8" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1187,6 +1259,21 @@
       <c r="AC9" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1295,6 +1382,21 @@
       <c r="AC10" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1403,6 +1505,21 @@
       <c r="AC11" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1511,6 +1628,21 @@
       <c r="AC12" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1619,6 +1751,21 @@
       <c r="AC13" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1727,6 +1874,21 @@
       <c r="AC14" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1835,6 +1997,21 @@
       <c r="AC15" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1943,6 +2120,21 @@
       <c r="AC16" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2051,6 +2243,21 @@
       <c r="AC17" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2159,6 +2366,21 @@
       <c r="AC18" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2267,6 +2489,21 @@
       <c r="AC19" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2375,6 +2612,21 @@
       <c r="AC20" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2483,6 +2735,21 @@
       <c r="AC21" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2591,6 +2858,21 @@
       <c r="AC22" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2699,6 +2981,21 @@
       <c r="AC23" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2807,6 +3104,21 @@
       <c r="AC24" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2915,6 +3227,21 @@
       <c r="AC25" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3023,6 +3350,21 @@
       <c r="AC26" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3131,6 +3473,21 @@
       <c r="AC27" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3239,6 +3596,21 @@
       <c r="AC28" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3347,6 +3719,21 @@
       <c r="AC29" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3455,6 +3842,21 @@
       <c r="AC30" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3563,6 +3965,21 @@
       <c r="AC31" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3671,6 +4088,21 @@
       <c r="AC32" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3779,6 +4211,21 @@
       <c r="AC33" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3887,6 +4334,21 @@
       <c r="AC34" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3995,6 +4457,21 @@
       <c r="AC35" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4103,6 +4580,21 @@
       <c r="AC36" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4211,6 +4703,21 @@
       <c r="AC37" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4319,6 +4826,21 @@
       <c r="AC38" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4427,6 +4949,21 @@
       <c r="AC39" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4535,6 +5072,21 @@
       <c r="AC40" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4643,6 +5195,21 @@
       <c r="AC41" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4751,6 +5318,21 @@
       <c r="AC42" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4859,6 +5441,21 @@
       <c r="AC43" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4967,6 +5564,21 @@
       <c r="AC44" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5075,6 +5687,21 @@
       <c r="AC45" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5183,6 +5810,21 @@
       <c r="AC46" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5291,6 +5933,21 @@
       <c r="AC47" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5399,6 +6056,21 @@
       <c r="AC48" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5507,6 +6179,21 @@
       <c r="AC49" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5615,6 +6302,21 @@
       <c r="AC50" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5723,6 +6425,21 @@
       <c r="AC51" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5831,6 +6548,21 @@
       <c r="AC52" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5939,6 +6671,21 @@
       <c r="AC53" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6047,6 +6794,21 @@
       <c r="AC54" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6155,6 +6917,21 @@
       <c r="AC55" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6263,6 +7040,21 @@
       <c r="AC56" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6371,6 +7163,21 @@
       <c r="AC57" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6479,6 +7286,21 @@
       <c r="AC58" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6587,6 +7409,21 @@
       <c r="AC59" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6695,6 +7532,21 @@
       <c r="AC60" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6803,6 +7655,21 @@
       <c r="AC61" t="n">
         <v>1</v>
       </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6911,6 +7778,21 @@
       <c r="AC62" t="n">
         <v>1</v>
       </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7019,6 +7901,21 @@
       <c r="AC63" t="n">
         <v>1</v>
       </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7127,6 +8024,21 @@
       <c r="AC64" t="n">
         <v>1</v>
       </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7235,6 +8147,21 @@
       <c r="AC65" t="n">
         <v>1</v>
       </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7343,6 +8270,21 @@
       <c r="AC66" t="n">
         <v>1</v>
       </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7451,6 +8393,21 @@
       <c r="AC67" t="n">
         <v>1</v>
       </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7559,6 +8516,21 @@
       <c r="AC68" t="n">
         <v>1</v>
       </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7667,6 +8639,21 @@
       <c r="AC69" t="n">
         <v>1</v>
       </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7775,6 +8762,21 @@
       <c r="AC70" t="n">
         <v>1</v>
       </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7883,6 +8885,21 @@
       <c r="AC71" t="n">
         <v>1</v>
       </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7991,6 +9008,21 @@
       <c r="AC72" t="n">
         <v>1</v>
       </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Bosch CL Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Bosch CL Series IOM</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Bosch CL Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8099,6 +9131,21 @@
       <c r="AC73" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8207,6 +9254,21 @@
       <c r="AC74" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8315,6 +9377,21 @@
       <c r="AC75" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8423,6 +9500,21 @@
       <c r="AC76" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8531,6 +9623,21 @@
       <c r="AC77" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8639,6 +9746,21 @@
       <c r="AC78" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8747,6 +9869,21 @@
       <c r="AC79" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8855,6 +9992,21 @@
       <c r="AC80" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8963,6 +10115,21 @@
       <c r="AC81" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9071,6 +10238,21 @@
       <c r="AC82" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9179,6 +10361,21 @@
       <c r="AC83" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9287,6 +10484,21 @@
       <c r="AC84" t="n">
         <v>0.25</v>
       </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9395,6 +10607,21 @@
       <c r="AC85" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9503,6 +10730,21 @@
       <c r="AC86" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9611,6 +10853,21 @@
       <c r="AC87" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9719,6 +10976,21 @@
       <c r="AC88" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9827,6 +11099,21 @@
       <c r="AC89" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9935,6 +11222,21 @@
       <c r="AC90" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10043,6 +11345,21 @@
       <c r="AC91" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10151,6 +11468,21 @@
       <c r="AC92" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10259,6 +11591,21 @@
       <c r="AC93" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10367,6 +11714,21 @@
       <c r="AC94" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10475,6 +11837,21 @@
       <c r="AC95" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10583,6 +11960,21 @@
       <c r="AC96" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10691,6 +12083,21 @@
       <c r="AC97" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10799,6 +12206,21 @@
       <c r="AC98" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10907,6 +12329,21 @@
       <c r="AC99" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11015,6 +12452,21 @@
       <c r="AC100" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11123,6 +12575,21 @@
       <c r="AC101" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11231,6 +12698,21 @@
       <c r="AC102" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11339,6 +12821,21 @@
       <c r="AC103" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11447,6 +12944,21 @@
       <c r="AC104" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11555,6 +13067,21 @@
       <c r="AC105" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11663,6 +13190,21 @@
       <c r="AC106" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11771,6 +13313,21 @@
       <c r="AC107" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11879,6 +13436,21 @@
       <c r="AC108" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11987,6 +13559,21 @@
       <c r="AC109" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12095,6 +13682,21 @@
       <c r="AC110" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12203,6 +13805,21 @@
       <c r="AC111" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -12311,6 +13928,21 @@
       <c r="AC112" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12419,6 +14051,21 @@
       <c r="AC113" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12527,6 +14174,21 @@
       <c r="AC114" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12635,6 +14297,21 @@
       <c r="AC115" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12743,6 +14420,21 @@
       <c r="AC116" t="n">
         <v>0.5</v>
       </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12851,6 +14543,21 @@
       <c r="AC117" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12959,6 +14666,21 @@
       <c r="AC118" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -13067,6 +14789,21 @@
       <c r="AC119" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -13175,6 +14912,21 @@
       <c r="AC120" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -13283,6 +15035,21 @@
       <c r="AC121" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -13391,6 +15158,21 @@
       <c r="AC122" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13499,6 +15281,21 @@
       <c r="AC123" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -13607,6 +15404,21 @@
       <c r="AC124" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13715,6 +15527,21 @@
       <c r="AC125" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13823,6 +15650,21 @@
       <c r="AC126" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13931,6 +15773,21 @@
       <c r="AC127" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14039,6 +15896,21 @@
       <c r="AC128" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14147,6 +16019,21 @@
       <c r="AC129" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14255,6 +16142,21 @@
       <c r="AC130" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -14363,6 +16265,21 @@
       <c r="AC131" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14471,6 +16388,21 @@
       <c r="AC132" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14579,6 +16511,21 @@
       <c r="AC133" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14687,6 +16634,21 @@
       <c r="AC134" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14795,6 +16757,21 @@
       <c r="AC135" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14903,6 +16880,21 @@
       <c r="AC136" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -15011,6 +17003,21 @@
       <c r="AC137" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15119,6 +17126,21 @@
       <c r="AC138" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -15227,6 +17249,21 @@
       <c r="AC139" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -15335,6 +17372,21 @@
       <c r="AC140" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -15443,6 +17495,21 @@
       <c r="AC141" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -15551,6 +17618,21 @@
       <c r="AC142" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15659,6 +17741,21 @@
       <c r="AC143" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15767,6 +17864,21 @@
       <c r="AC144" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15875,6 +17987,21 @@
       <c r="AC145" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15983,6 +18110,21 @@
       <c r="AC146" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -16091,6 +18233,21 @@
       <c r="AC147" t="n">
         <v>1</v>
       </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -16199,6 +18356,21 @@
       <c r="AC148" t="n">
         <v>1</v>
       </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -16307,6 +18479,21 @@
       <c r="AC149" t="n">
         <v>1</v>
       </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -16415,6 +18602,21 @@
       <c r="AC150" t="n">
         <v>1</v>
       </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -16523,6 +18725,21 @@
       <c r="AC151" t="n">
         <v>1</v>
       </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -16631,6 +18848,21 @@
       <c r="AC152" t="n">
         <v>1</v>
       </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -16739,6 +18971,21 @@
       <c r="AC153" t="n">
         <v>1</v>
       </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -16847,6 +19094,21 @@
       <c r="AC154" t="n">
         <v>1</v>
       </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16955,6 +19217,21 @@
       <c r="AC155" t="n">
         <v>1</v>
       </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -17063,6 +19340,21 @@
       <c r="AC156" t="n">
         <v>1</v>
       </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -17171,6 +19463,21 @@
       <c r="AC157" t="n">
         <v>1</v>
       </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -17279,6 +19586,21 @@
       <c r="AC158" t="n">
         <v>1</v>
       </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -17387,6 +19709,21 @@
       <c r="AC159" t="n">
         <v>1</v>
       </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -17495,6 +19832,21 @@
       <c r="AC160" t="n">
         <v>1</v>
       </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -17603,6 +19955,21 @@
       <c r="AC161" t="n">
         <v>1</v>
       </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -17711,6 +20078,21 @@
       <c r="AC162" t="n">
         <v>1</v>
       </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -17819,6 +20201,21 @@
       <c r="AC163" t="n">
         <v>1</v>
       </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -17927,6 +20324,21 @@
       <c r="AC164" t="n">
         <v>1</v>
       </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>Bosch CF Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>Bosch CF Series IOM</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>Bosch CF Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -18035,6 +20447,21 @@
       <c r="AC165" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -18143,6 +20570,21 @@
       <c r="AC166" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -18251,6 +20693,21 @@
       <c r="AC167" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -18359,6 +20816,21 @@
       <c r="AC168" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -18467,6 +20939,21 @@
       <c r="AC169" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -18575,6 +21062,21 @@
       <c r="AC170" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -18683,6 +21185,21 @@
       <c r="AC171" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -18791,6 +21308,21 @@
       <c r="AC172" t="n">
         <v>0.33</v>
       </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -18899,6 +21431,21 @@
       <c r="AC173" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -19007,6 +21554,21 @@
       <c r="AC174" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -19115,6 +21677,21 @@
       <c r="AC175" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -19223,6 +21800,21 @@
       <c r="AC176" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -19331,6 +21923,21 @@
       <c r="AC177" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -19439,6 +22046,21 @@
       <c r="AC178" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -19547,6 +22169,21 @@
       <c r="AC179" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -19655,6 +22292,21 @@
       <c r="AC180" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -19763,6 +22415,21 @@
       <c r="AC181" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -19871,6 +22538,21 @@
       <c r="AC182" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -19979,6 +22661,21 @@
       <c r="AC183" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -20087,6 +22784,21 @@
       <c r="AC184" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -20195,6 +22907,21 @@
       <c r="AC185" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -20303,6 +23030,21 @@
       <c r="AC186" t="n">
         <v>0.75</v>
       </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -20411,6 +23153,21 @@
       <c r="AC187" t="n">
         <v>1</v>
       </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -20519,6 +23276,21 @@
       <c r="AC188" t="n">
         <v>1</v>
       </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -20627,6 +23399,21 @@
       <c r="AC189" t="n">
         <v>1</v>
       </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -20735,6 +23522,21 @@
       <c r="AC190" t="n">
         <v>1</v>
       </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -20843,6 +23645,21 @@
       <c r="AC191" t="n">
         <v>1</v>
       </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -20951,6 +23768,21 @@
       <c r="AC192" t="n">
         <v>1</v>
       </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -21059,6 +23891,21 @@
       <c r="AC193" t="n">
         <v>1</v>
       </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -21167,6 +24014,21 @@
       <c r="AC194" t="n">
         <v>1</v>
       </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -21275,6 +24137,21 @@
       <c r="AC195" t="n">
         <v>1</v>
       </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -21383,6 +24260,21 @@
       <c r="AC196" t="n">
         <v>1</v>
       </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -21491,6 +24383,21 @@
       <c r="AC197" t="n">
         <v>1</v>
       </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -21599,6 +24506,21 @@
       <c r="AC198" t="n">
         <v>1</v>
       </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>Bosch CP Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Bosch CP Series IOM</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>Bosch CP Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -21707,6 +24629,21 @@
       <c r="AC199" t="n">
         <v>1</v>
       </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -21815,6 +24752,21 @@
       <c r="AC200" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -21923,6 +24875,21 @@
       <c r="AC201" t="n">
         <v>2</v>
       </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -22031,6 +24998,21 @@
       <c r="AC202" t="n">
         <v>1</v>
       </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -22139,6 +25121,21 @@
       <c r="AC203" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -22247,6 +25244,21 @@
       <c r="AC204" t="n">
         <v>2</v>
       </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -22355,6 +25367,21 @@
       <c r="AC205" t="n">
         <v>3</v>
       </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -22463,6 +25490,21 @@
       <c r="AC206" t="n">
         <v>1</v>
       </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -22571,6 +25613,21 @@
       <c r="AC207" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -22679,6 +25736,21 @@
       <c r="AC208" t="n">
         <v>2</v>
       </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -22787,6 +25859,21 @@
       <c r="AC209" t="n">
         <v>3</v>
       </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -22895,6 +25982,21 @@
       <c r="AC210" t="n">
         <v>1</v>
       </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -23003,6 +26105,21 @@
       <c r="AC211" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -23111,6 +26228,21 @@
       <c r="AC212" t="n">
         <v>2</v>
       </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -23219,6 +26351,21 @@
       <c r="AC213" t="n">
         <v>1</v>
       </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -23327,6 +26474,21 @@
       <c r="AC214" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -23435,6 +26597,21 @@
       <c r="AC215" t="n">
         <v>2</v>
       </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -23543,6 +26720,21 @@
       <c r="AC216" t="n">
         <v>3</v>
       </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -23651,6 +26843,21 @@
       <c r="AC217" t="n">
         <v>1</v>
       </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -23759,6 +26966,21 @@
       <c r="AC218" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -23867,6 +27089,21 @@
       <c r="AC219" t="n">
         <v>2</v>
       </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -23975,6 +27212,21 @@
       <c r="AC220" t="n">
         <v>3</v>
       </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -24083,6 +27335,21 @@
       <c r="AC221" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -24191,6 +27458,21 @@
       <c r="AC222" t="n">
         <v>2</v>
       </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -24299,6 +27581,21 @@
       <c r="AC223" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -24407,6 +27704,21 @@
       <c r="AC224" t="n">
         <v>2</v>
       </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -24515,6 +27827,21 @@
       <c r="AC225" t="n">
         <v>3</v>
       </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -24623,6 +27950,21 @@
       <c r="AC226" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -24731,6 +28073,21 @@
       <c r="AC227" t="n">
         <v>2</v>
       </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -24839,6 +28196,21 @@
       <c r="AC228" t="n">
         <v>3</v>
       </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -24947,6 +28319,21 @@
       <c r="AC229" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -25055,6 +28442,21 @@
       <c r="AC230" t="n">
         <v>2</v>
       </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -25163,6 +28565,21 @@
       <c r="AC231" t="n">
         <v>3</v>
       </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -25271,6 +28688,21 @@
       <c r="AC232" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -25379,6 +28811,21 @@
       <c r="AC233" t="n">
         <v>2</v>
       </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -25487,6 +28934,21 @@
       <c r="AC234" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -25595,6 +29057,21 @@
       <c r="AC235" t="n">
         <v>2</v>
       </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -25703,6 +29180,21 @@
       <c r="AC236" t="n">
         <v>3</v>
       </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -25811,6 +29303,21 @@
       <c r="AC237" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -25919,6 +29426,21 @@
       <c r="AC238" t="n">
         <v>2</v>
       </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -26027,6 +29549,21 @@
       <c r="AC239" t="n">
         <v>3</v>
       </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -26135,6 +29672,21 @@
       <c r="AC240" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -26243,6 +29795,21 @@
       <c r="AC241" t="n">
         <v>2</v>
       </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -26351,6 +29918,21 @@
       <c r="AC242" t="n">
         <v>3</v>
       </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -26459,6 +30041,21 @@
       <c r="AC243" t="n">
         <v>2</v>
       </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -26567,6 +30164,21 @@
       <c r="AC244" t="n">
         <v>2</v>
       </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -26675,6 +30287,21 @@
       <c r="AC245" t="n">
         <v>3</v>
       </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -26783,6 +30410,21 @@
       <c r="AC246" t="n">
         <v>5</v>
       </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -26891,6 +30533,21 @@
       <c r="AC247" t="n">
         <v>2</v>
       </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -26999,6 +30656,21 @@
       <c r="AC248" t="n">
         <v>3</v>
       </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -27107,6 +30779,21 @@
       <c r="AC249" t="n">
         <v>5</v>
       </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -27215,6 +30902,21 @@
       <c r="AC250" t="n">
         <v>2</v>
       </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -27323,6 +31025,21 @@
       <c r="AC251" t="n">
         <v>3</v>
       </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -27431,6 +31148,21 @@
       <c r="AC252" t="n">
         <v>5</v>
       </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -27539,6 +31271,21 @@
       <c r="AC253" t="n">
         <v>3</v>
       </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -27647,6 +31394,21 @@
       <c r="AC254" t="n">
         <v>5</v>
       </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -27755,6 +31517,21 @@
       <c r="AC255" t="n">
         <v>3</v>
       </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -27863,6 +31640,21 @@
       <c r="AC256" t="n">
         <v>5</v>
       </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -27971,6 +31763,21 @@
       <c r="AC257" t="n">
         <v>3</v>
       </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -28079,6 +31886,21 @@
       <c r="AC258" t="n">
         <v>5</v>
       </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -28187,6 +32009,21 @@
       <c r="AC259" t="n">
         <v>3</v>
       </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -28295,6 +32132,21 @@
       <c r="AC260" t="n">
         <v>5</v>
       </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -28403,6 +32255,21 @@
       <c r="AC261" t="n">
         <v>3</v>
       </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -28511,6 +32378,21 @@
       <c r="AC262" t="n">
         <v>5</v>
       </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -28619,6 +32501,21 @@
       <c r="AC263" t="n">
         <v>3</v>
       </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -28727,6 +32624,21 @@
       <c r="AC264" t="n">
         <v>5</v>
       </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -28835,6 +32747,21 @@
       <c r="AC265" t="n">
         <v>3</v>
       </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -28943,6 +32870,21 @@
       <c r="AC266" t="n">
         <v>5</v>
       </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -29051,6 +32993,21 @@
       <c r="AC267" t="n">
         <v>3</v>
       </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -29159,6 +33116,21 @@
       <c r="AC268" t="n">
         <v>5</v>
       </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -29267,6 +33239,21 @@
       <c r="AC269" t="n">
         <v>3</v>
       </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -29375,6 +33362,21 @@
       <c r="AC270" t="n">
         <v>5</v>
       </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -29483,6 +33485,21 @@
       <c r="AC271" t="n">
         <v>2</v>
       </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -29591,6 +33608,21 @@
       <c r="AC272" t="n">
         <v>3</v>
       </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -29699,6 +33731,21 @@
       <c r="AC273" t="n">
         <v>5</v>
       </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -29807,6 +33854,21 @@
       <c r="AC274" t="n">
         <v>2</v>
       </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -29915,6 +33977,21 @@
       <c r="AC275" t="n">
         <v>3</v>
       </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -30023,6 +34100,21 @@
       <c r="AC276" t="n">
         <v>5</v>
       </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -30131,6 +34223,21 @@
       <c r="AC277" t="n">
         <v>2</v>
       </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -30239,6 +34346,21 @@
       <c r="AC278" t="n">
         <v>3</v>
       </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -30347,6 +34469,21 @@
       <c r="AC279" t="n">
         <v>5</v>
       </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -30455,6 +34592,21 @@
       <c r="AC280" t="n">
         <v>5</v>
       </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -30563,6 +34715,21 @@
       <c r="AC281" t="n">
         <v>5</v>
       </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -30671,6 +34838,21 @@
       <c r="AC282" t="n">
         <v>5</v>
       </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -30779,6 +34961,21 @@
       <c r="AC283" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -30887,6 +35084,21 @@
       <c r="AC284" t="n">
         <v>2</v>
       </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -30995,6 +35207,21 @@
       <c r="AC285" t="n">
         <v>3</v>
       </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -31103,6 +35330,21 @@
       <c r="AC286" t="n">
         <v>5</v>
       </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -31211,6 +35453,21 @@
       <c r="AC287" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -31319,6 +35576,21 @@
       <c r="AC288" t="n">
         <v>2</v>
       </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -31427,6 +35699,21 @@
       <c r="AC289" t="n">
         <v>3</v>
       </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -31535,6 +35822,21 @@
       <c r="AC290" t="n">
         <v>5</v>
       </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -31643,6 +35945,21 @@
       <c r="AC291" t="n">
         <v>1.5</v>
       </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -31751,6 +36068,21 @@
       <c r="AC292" t="n">
         <v>2</v>
       </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -31859,6 +36191,21 @@
       <c r="AC293" t="n">
         <v>3</v>
       </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -31967,6 +36314,21 @@
       <c r="AC294" t="n">
         <v>5</v>
       </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG294" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH294" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -32075,6 +36437,21 @@
       <c r="AC295" t="n">
         <v>2</v>
       </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -32183,6 +36560,21 @@
       <c r="AC296" t="n">
         <v>3</v>
       </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH296" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -32291,6 +36683,21 @@
       <c r="AC297" t="n">
         <v>5</v>
       </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -32399,6 +36806,21 @@
       <c r="AC298" t="n">
         <v>2</v>
       </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -32507,6 +36929,21 @@
       <c r="AC299" t="n">
         <v>3</v>
       </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -32615,6 +37052,21 @@
       <c r="AC300" t="n">
         <v>5</v>
       </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -32723,6 +37175,21 @@
       <c r="AC301" t="n">
         <v>2</v>
       </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -32831,6 +37298,21 @@
       <c r="AC302" t="n">
         <v>3</v>
       </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -32939,6 +37421,21 @@
       <c r="AC303" t="n">
         <v>5</v>
       </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -33047,6 +37544,21 @@
       <c r="AC304" t="n">
         <v>2</v>
       </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG304" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH304" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -33155,6 +37667,21 @@
       <c r="AC305" t="n">
         <v>3</v>
       </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -33263,6 +37790,21 @@
       <c r="AC306" t="n">
         <v>5</v>
       </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -33371,6 +37913,21 @@
       <c r="AC307" t="n">
         <v>2</v>
       </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -33479,6 +38036,21 @@
       <c r="AC308" t="n">
         <v>3</v>
       </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -33587,6 +38159,21 @@
       <c r="AC309" t="n">
         <v>5</v>
       </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -33695,6 +38282,21 @@
       <c r="AC310" t="n">
         <v>2</v>
       </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG310" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -33803,6 +38405,21 @@
       <c r="AC311" t="n">
         <v>3</v>
       </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -33911,6 +38528,21 @@
       <c r="AC312" t="n">
         <v>5</v>
       </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -34019,6 +38651,21 @@
       <c r="AC313" t="n">
         <v>3</v>
       </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -34127,6 +38774,21 @@
       <c r="AC314" t="n">
         <v>5</v>
       </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -34235,6 +38897,21 @@
       <c r="AC315" t="n">
         <v>3</v>
       </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -34343,6 +39020,21 @@
       <c r="AC316" t="n">
         <v>5</v>
       </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -34451,6 +39143,21 @@
       <c r="AC317" t="n">
         <v>3</v>
       </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -34559,6 +39266,21 @@
       <c r="AC318" t="n">
         <v>5</v>
       </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -34667,6 +39389,21 @@
       <c r="AC319" t="n">
         <v>5</v>
       </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -34775,6 +39512,21 @@
       <c r="AC320" t="n">
         <v>5</v>
       </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -34883,14 +39635,30 @@
       <c r="AC321" t="n">
         <v>5</v>
       </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>Bosch EC Engineering Submittal 09.2026</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>Bosch EC Series IOM</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>Bosch EC Series Revit Families</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="M3:P3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="AH2:AH4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="AA2:AA4"/>
     <mergeCell ref="D3:D4"/>
@@ -34898,17 +39666,18 @@
     <mergeCell ref="X2:X4"/>
     <mergeCell ref="X1:AC1"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="I3:L3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="V3:V4"/>
+    <mergeCell ref="AG2:AG4"/>
     <mergeCell ref="Y2:Y4"/>
     <mergeCell ref="AE2:AE4"/>
     <mergeCell ref="Z2:Z4"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="AB2:AB4"/>
     <mergeCell ref="F3:H3"/>
+    <mergeCell ref="AE1:AH1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34999,9 +39768,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
